--- a/services_forms/018_haulout_service_agreement--services_forms.xlsx
+++ b/services_forms/018_haulout_service_agreement--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1364,17 +1364,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>haulout_services_choices</t>
+          <t>haulout_service_agreement_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>haulout_and_launching_and_painting</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Haulout and Launching and Painting</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>haulout_service_agreement_choices</t>
+          <t>vessel_status_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>in_haulout_process</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>In Haulout Process</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>in_haulout_process</t>
+          <t>in_storage</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>In Haulout Process</t>
+          <t>In Storage</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>in_storage</t>
+          <t>under_contract</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>In Storage</t>
+          <t>Under Contract</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>under_contract</t>
+          <t>under_survey</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Under Contract</t>
+          <t>Under Survey</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>under_survey</t>
+          <t>out_of_contract</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Under Survey</t>
+          <t>Out of Contract</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>vessel_status_choices</t>
+          <t>haulout_status_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>out_of_contract</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Out of Contract</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>haulout_status_choices</t>
+          <t>vessel_type_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Boat</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>yacht</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Yacht</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yacht</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yacht</t>
+          <t>Sailboat</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sailboat</t>
+          <t>ship</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sailboat</t>
+          <t>Ship</t>
         </is>
       </c>
     </row>
@@ -1607,27 +1607,10 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ship</t>
+          <t>vessel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>Ship</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>vessel_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>vessel</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>Vessel</t>
         </is>
